--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90568872</v>
+        <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>102464</v>
+        <v>99261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>219788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skålbergsmyren, väg W889, Dlr</t>
+          <t>Sandviken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521164</v>
+        <v>521257</v>
       </c>
       <c r="R2" t="n">
-        <v>6765639</v>
+        <v>6765642</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca 1m^2</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,39 +767,2169 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936667</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136933253</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>520558</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6765623</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933253</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136933258</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520484</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6765585</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933258</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136936658</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520964</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6765659</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936658</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136936659</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6765654</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936659</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136936660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>521245</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6765654</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136936661</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>521261</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6765653</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936661</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136936662</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>521286</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6765652</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936662</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136936664</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>521286</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6765642</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936664</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136936665</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>521281</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6765643</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936665</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136936668</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>521249</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6765642</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936668</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136936669</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>521235</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6765641</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936669</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136936670</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521034</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6765643</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936670</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136933252</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99388</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>520706</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6765653</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933252</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>90568872</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skålbergsmyren, väg W889, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521164</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6765639</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-06-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-06-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ca 1m^2</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Leif Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Emma Karlsson, Therese Kalling</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/90568872</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136933254</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>520569</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6765627</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933254</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136933259</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99263</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>520516</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6765592</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933259</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136933251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>520730</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6765652</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933251</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136933255</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ol-Ersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>520548</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6765605</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933255</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136936666</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sandviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521276</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6765642</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136936666</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99261</v>
+        <v>99267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99263</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99267</v>
+        <v>99269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99269</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99272</v>
+        <v>99278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99278</v>
+        <v>99282</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99280</v>
+        <v>99282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99282</v>
+        <v>99284</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99282</v>
+        <v>99284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99284</v>
+        <v>99297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99286</v>
+        <v>99299</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99297</v>
+        <v>99299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99299</v>
+        <v>99301</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99299</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99301</v>
+        <v>99304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99304</v>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99312</v>
+        <v>99313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99315</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99313</v>
+        <v>99318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99315</v>
+        <v>99320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99318</v>
+        <v>99320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99320</v>
+        <v>99322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99322</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99326</v>
+        <v>99338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99328</v>
+        <v>99340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99338</v>
+        <v>99339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99340</v>
+        <v>99341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99341</v>
+        <v>99344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99342</v>
+        <v>99343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15164-2026 artfynd.xlsx
+++ b/artfynd/A 15164-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936667</v>
       </c>
       <c r="B2" t="n">
-        <v>99343</v>
+        <v>99346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136933253</v>
       </c>
       <c r="B3" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136933258</v>
       </c>
       <c r="B4" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136936658</v>
       </c>
       <c r="B5" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>136936659</v>
       </c>
       <c r="B6" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136936660</v>
       </c>
       <c r="B7" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136936661</v>
       </c>
       <c r="B8" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>136936662</v>
       </c>
       <c r="B9" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136936664</v>
       </c>
       <c r="B10" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136936665</v>
       </c>
       <c r="B11" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>136936668</v>
       </c>
       <c r="B12" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>136936669</v>
       </c>
       <c r="B13" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>136936670</v>
       </c>
       <c r="B14" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136933252</v>
       </c>
       <c r="B15" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>136933254</v>
       </c>
       <c r="B17" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>136933259</v>
       </c>
       <c r="B18" t="n">
-        <v>99345</v>
+        <v>99348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136933251</v>
       </c>
       <c r="B19" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136933255</v>
       </c>
       <c r="B20" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136936666</v>
       </c>
       <c r="B21" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
